--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Pathogenic Agents</t>
+    <t>Pathogenic Agents list</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Pregnancy Codes - used for EHRs to consider pregnancy status</t>
+    <t>Pathogenic agent codes</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/ValueSet/PathogenicAgents</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/ValueSet/PathogenicAgents</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:59:35+00:00</t>
+    <t>2025-03-07T09:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:27:46+00:00</t>
+    <t>2025-03-11T13:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,13 @@
     <t>234</t>
   </si>
   <si>
+    <t>Gonokocus</t>
+  </si>
+  <si>
     <t>345</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
   <si>
     <t/>
@@ -417,28 +423,32 @@
       <c r="A3" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-11T13:27:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-PathogenicAgents.xlsx
+++ b/ValueSet-PathogenicAgents.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
